--- a/data/trans_camb/P74B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 12,87</t>
+          <t>1,72; 12,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 7,08</t>
+          <t>-2,37; 7,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,15; -15,93</t>
+          <t>-33,66; -16,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,8; -9,34</t>
+          <t>-27,07; -9,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 7,11</t>
+          <t>-5,73; 6,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 8,24</t>
+          <t>-3,48; 7,64</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,29; 182,53</t>
+          <t>14,43; 184,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 101,6</t>
+          <t>-22,6; 113,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,25; -19,97</t>
+          <t>-38,81; -19,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,88; -11,51</t>
+          <t>-30,97; -12,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 24,03</t>
+          <t>-16,03; 22,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 27,99</t>
+          <t>-9,87; 25,88</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 8,95</t>
+          <t>0,23; 8,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,9</t>
+          <t>0,94; 9,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,09; -12,02</t>
+          <t>-27,45; -10,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,54; -13,5</t>
+          <t>-29,16; -13,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 9,75</t>
+          <t>-1,33; 9,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 9,84</t>
+          <t>-0,99; 10,01</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 141,25</t>
+          <t>1,15; 139,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 153,35</t>
+          <t>8,17; 161,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,95; -14,6</t>
+          <t>-31,05; -13,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,31; -16,3</t>
+          <t>-33,13; -17,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 35,72</t>
+          <t>-3,76; 35,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 36,15</t>
+          <t>-2,76; 37,21</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,61</t>
+          <t>1,18; 10,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 7,31</t>
+          <t>-0,93; 6,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -1,37</t>
+          <t>-20,83; -1,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,66; -6,18</t>
+          <t>-25,1; -6,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 14,03</t>
+          <t>1,91; 14,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 9,07</t>
+          <t>-2,06; 9,6</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,08; 340,21</t>
+          <t>13,93; 300,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 216,98</t>
+          <t>-18,58; 192,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,08; -1,72</t>
+          <t>-24,97; -1,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,11; -8,57</t>
+          <t>-30,46; -8,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 60,69</t>
+          <t>6,58; 62,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 38,09</t>
+          <t>-7,21; 43,24</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 7,77</t>
+          <t>-1,39; 8,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 13,15</t>
+          <t>3,67; 13,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 5,36</t>
+          <t>-11,92; 4,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 0,16</t>
+          <t>-18,11; -0,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 10,36</t>
+          <t>-0,7; 10,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 9,41</t>
+          <t>-2,38; 8,9</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 127,36</t>
+          <t>-14,43; 133,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,89; 239,76</t>
+          <t>34,74; 229,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 6,91</t>
+          <t>-14,18; 6,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 0,22</t>
+          <t>-21,57; -0,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 34,13</t>
+          <t>-2,37; 34,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 31,12</t>
+          <t>-6,89; 29,15</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,45</t>
+          <t>2,67; 7,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,22</t>
+          <t>2,51; 7,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -10,59</t>
+          <t>-18,68; -10,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,3; -12,08</t>
+          <t>-21,04; -12,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,47</t>
+          <t>1,65; 7,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,24</t>
+          <t>0,42; 6,33</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>28,74; 115,32</t>
+          <t>30,2; 109,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,16; 111,49</t>
+          <t>31,15; 110,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,32; -12,99</t>
+          <t>-22,16; -12,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,17; -14,89</t>
+          <t>-24,97; -14,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,59; 25,72</t>
+          <t>5,23; 25,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,58; 21,55</t>
+          <t>1,4; 21,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P74B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,65</t>
+          <t>1,47; 12,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 7,31</t>
+          <t>-2,19; 7,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,66; -16,01</t>
+          <t>-34,06; -14,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,07; -9,89</t>
+          <t>-27,81; -10,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 6,59</t>
+          <t>-5,0; 6,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 7,64</t>
+          <t>-3,51; 8,05</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 184,72</t>
+          <t>12,15; 183,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 113,07</t>
+          <t>-21,0; 104,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,81; -19,56</t>
+          <t>-38,96; -17,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,97; -12,33</t>
+          <t>-31,6; -12,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 22,25</t>
+          <t>-14,0; 21,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 25,88</t>
+          <t>-9,88; 27,12</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 8,82</t>
+          <t>0,2; 8,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,73</t>
+          <t>1,38; 10,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,45; -10,99</t>
+          <t>-28,03; -10,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -13,75</t>
+          <t>-28,85; -12,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 9,39</t>
+          <t>-1,32; 9,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 10,01</t>
+          <t>-0,7; 10,18</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 139,66</t>
+          <t>0,01; 136,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 161,91</t>
+          <t>11,16; 175,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,05; -13,52</t>
+          <t>-31,67; -13,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,13; -17,27</t>
+          <t>-33,0; -15,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 35,25</t>
+          <t>-4,61; 35,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 37,21</t>
+          <t>-2,11; 37,15</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,51</t>
+          <t>1,66; 11,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 6,81</t>
+          <t>-1,02; 6,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -1,5</t>
+          <t>-21,22; -1,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,1; -6,64</t>
+          <t>-26,87; -6,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 14,17</t>
+          <t>1,68; 14,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 9,6</t>
+          <t>-1,82; 8,94</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,93; 300,69</t>
+          <t>21,84; 335,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 192,16</t>
+          <t>-17,54; 211,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -1,9</t>
+          <t>-25,15; -1,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,46; -8,99</t>
+          <t>-32,61; -9,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 62,65</t>
+          <t>6,13; 62,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 43,24</t>
+          <t>-6,49; 40,06</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 8,0</t>
+          <t>-0,99; 8,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 13,13</t>
+          <t>3,55; 12,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 4,59</t>
+          <t>-11,62; 4,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,11; -0,69</t>
+          <t>-18,66; -0,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 10,53</t>
+          <t>-0,8; 10,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 8,9</t>
+          <t>-2,08; 9,48</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 133,24</t>
+          <t>-11,99; 147,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,74; 229,66</t>
+          <t>32,07; 210,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 6,04</t>
+          <t>-13,8; 5,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -0,96</t>
+          <t>-22,32; -1,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 34,36</t>
+          <t>-2,09; 36,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 29,15</t>
+          <t>-5,28; 30,97</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,2</t>
+          <t>2,53; 7,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,31</t>
+          <t>2,71; 7,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,68; -10,18</t>
+          <t>-19,22; -10,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,04; -12,02</t>
+          <t>-21,07; -11,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,39</t>
+          <t>1,59; 7,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,33</t>
+          <t>0,49; 6,06</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30,2; 109,08</t>
+          <t>29,53; 110,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,15; 110,36</t>
+          <t>30,53; 111,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -12,55</t>
+          <t>-22,67; -12,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -14,84</t>
+          <t>-24,95; -14,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,23; 25,55</t>
+          <t>4,97; 25,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,4; 21,78</t>
+          <t>1,68; 21,29</t>
         </is>
       </c>
     </row>
